--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -48,7 +48,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dynamic FX · 5bp</t>
+          <t>PDS + Dynamic FX (5bp)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -79,13 +79,13 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.02865984633458529</v>
+        <v>0.03480731918133273</v>
       </c>
       <c r="C2" s="1">
-        <v>0.05115615440670096</v>
+        <v>0.0574380695994956</v>
       </c>
       <c r="D2" s="1">
-        <v>0.07164132906138332</v>
+        <v>0.09694350871302371</v>
       </c>
       <c r="E2" s="1">
         <v>0.04437253533451946</v>
@@ -103,13 +103,13 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.06027352403745478</v>
+        <v>-0.05786895544144621</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.05282400320937097</v>
+        <v>-0.05040037280729803</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.0813899042759948</v>
+        <v>-0.07173192787694704</v>
       </c>
       <c r="E3" s="1">
         <v>-0.04327051572324403</v>
@@ -127,10 +127,10 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.006349162632413363</v>
+        <v>-0.006349162632414029</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02348466728004617</v>
+        <v>-0.02348466728004661</v>
       </c>
       <c r="D4" s="1">
         <v>-0.03191397779272764</v>
@@ -151,13 +151,13 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07552316304537787</v>
+        <v>0.07552316304537832</v>
       </c>
       <c r="C5" s="1">
-        <v>0.0680822510844179</v>
+        <v>0.06808225108441812</v>
       </c>
       <c r="D5" s="1">
-        <v>0.08241348173635243</v>
+        <v>0.08241348173635221</v>
       </c>
       <c r="E5" s="1">
         <v>0.06328153206946352</v>
@@ -175,13 +175,13 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.08286669498855148</v>
+        <v>0.08283399502926669</v>
       </c>
       <c r="C6" s="1">
-        <v>0.09369335078245644</v>
+        <v>0.09366032388431056</v>
       </c>
       <c r="D6" s="1">
-        <v>0.138116221557653</v>
+        <v>0.1379985506159107</v>
       </c>
       <c r="E6" s="1">
         <v>0.07894707047686933</v>
@@ -199,13 +199,13 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.05292396020991308</v>
+        <v>-0.0525388215458209</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07554630879154212</v>
+        <v>-0.07517036974896418</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.08804818870189246</v>
+        <v>-0.0864924086562967</v>
       </c>
       <c r="E7" s="1">
         <v>-0.07137572261430858</v>
@@ -223,13 +223,13 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.04855655795233171</v>
+        <v>0.05355636201714331</v>
       </c>
       <c r="C8" s="1">
-        <v>0.04750981875209215</v>
+        <v>0.05250463167849762</v>
       </c>
       <c r="D8" s="1">
-        <v>0.008834524013307865</v>
+        <v>0.02882602930971068</v>
       </c>
       <c r="E8" s="1">
         <v>0.06040569932885687</v>
@@ -247,13 +247,13 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07073007740498083</v>
+        <v>0.07131811233513297</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07442562966675537</v>
+        <v>0.07501569415959697</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06745922795148496</v>
+        <v>0.06981911240614602</v>
       </c>
       <c r="E9" s="1">
         <v>0.07672064779432697</v>
@@ -271,13 +271,13 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01172031519172112</v>
+        <v>0.01172032135908996</v>
       </c>
       <c r="C10" s="1">
-        <v>0.0201407739614734</v>
+        <v>0.02014078018017185</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426738196587452</v>
+        <v>0.02426740697417418</v>
       </c>
       <c r="E10" s="1">
         <v>0.01875736131405326</v>
@@ -295,13 +295,13 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01148210469120681</v>
+        <v>0.01166436280053529</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.001367367880744985</v>
+        <v>-0.001187425107066598</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.005218051108377031</v>
+        <v>-0.004492457278143069</v>
       </c>
       <c r="E11" s="1">
         <v>-8.422169188504469e-05</v>
@@ -319,13 +319,13 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.04945256734711112</v>
+        <v>0.05056190453239551</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04196369833249625</v>
+        <v>0.04306511931353163</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03462977045244275</v>
+        <v>0.03904012692536307</v>
       </c>
       <c r="E12" s="1">
         <v>0.044410290250674</v>
@@ -343,13 +343,13 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07400328952065482</v>
+        <v>0.07355902411024573</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06707176895797518</v>
+        <v>0.06663037079653833</v>
       </c>
       <c r="D13" s="1">
-        <v>0.08054512040851125</v>
+        <v>0.07878106091421655</v>
       </c>
       <c r="E13" s="1">
         <v>0.06259113492093893</v>
@@ -387,7 +387,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F2R 25% + ADAA 75% fixed over displayed history</t>
+          <t>Governed strategic allocation; exact provider composition private</t>
         </is>
       </c>
     </row>
@@ -423,7 +423,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SlackQuant PDS public-safe governed export</t>
+          <t>Source-owned PDS public-safe governed export</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CSV SHA256</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>d527da8625755b4774c7423c97275c86e56dd3fbd0960e5d9962779502e420ba</t>
         </is>
       </c>
     </row>

--- a/public/data/systems/pds/public_recent_12m_returns.xlsx
+++ b/public/data/systems/pds/public_recent_12m_returns.xlsx
@@ -79,16 +79,16 @@
         </is>
       </c>
       <c r="B2" s="1">
-        <v>0.03480731918133273</v>
+        <v>0.03480732327257319</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0574380695994956</v>
+        <v>0.0574380737802096</v>
       </c>
       <c r="D2" s="1">
         <v>0.09694350871302371</v>
       </c>
       <c r="E2" s="1">
-        <v>0.04437253533451946</v>
+        <v>0.04437254080456055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -103,16 +103,16 @@
         </is>
       </c>
       <c r="B3" s="1">
-        <v>-0.05786895544144621</v>
+        <v>-0.05786896499436156</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.05040037280729803</v>
+        <v>-0.05040038243594258</v>
       </c>
       <c r="D3" s="1">
         <v>-0.07173192787694704</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.04327051572324403</v>
+        <v>-0.04327052859411606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -127,16 +127,16 @@
         </is>
       </c>
       <c r="B4" s="1">
-        <v>-0.006349162632414029</v>
+        <v>-0.006349158442716551</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.02348466728004661</v>
+        <v>-0.02348466316260089</v>
       </c>
       <c r="D4" s="1">
         <v>-0.03191397779272764</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.02069781260823889</v>
+        <v>-0.02069780714412506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -151,16 +151,16 @@
         </is>
       </c>
       <c r="B5" s="1">
-        <v>0.07552316304537832</v>
+        <v>0.07552317289300148</v>
       </c>
       <c r="C5" s="1">
-        <v>0.06808225108441812</v>
+        <v>0.06808226086391156</v>
       </c>
       <c r="D5" s="1">
         <v>0.08241348173635221</v>
       </c>
       <c r="E5" s="1">
-        <v>0.06328153206946352</v>
+        <v>0.06328154521851803</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -175,16 +175,16 @@
         </is>
       </c>
       <c r="B6" s="1">
-        <v>0.08283399502926669</v>
+        <v>0.08283398244173745</v>
       </c>
       <c r="C6" s="1">
-        <v>0.09366032388431056</v>
+        <v>0.09366031117092977</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1379985506159107</v>
+        <v>0.1379985504593355</v>
       </c>
       <c r="E6" s="1">
-        <v>0.07894707047686933</v>
+        <v>0.07894705376009514</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -199,16 +199,16 @@
         </is>
       </c>
       <c r="B7" s="1">
-        <v>-0.0525388215458209</v>
+        <v>-0.05253881478963929</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.07517036974896418</v>
+        <v>-0.07517036315416503</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.0864924086562967</v>
+        <v>-0.08649242841708982</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.07137572261430858</v>
+        <v>-0.07137570738535337</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -223,16 +223,16 @@
         </is>
       </c>
       <c r="B8" s="1">
-        <v>0.05355636201714331</v>
+        <v>0.05355638169302601</v>
       </c>
       <c r="C8" s="1">
-        <v>0.05250463167849762</v>
+        <v>0.05250465133473847</v>
       </c>
       <c r="D8" s="1">
-        <v>0.02882602930971068</v>
+        <v>0.02882605578313768</v>
       </c>
       <c r="E8" s="1">
-        <v>0.06040569932885687</v>
+        <v>0.06040571692215058</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -247,16 +247,16 @@
         </is>
       </c>
       <c r="B9" s="1">
-        <v>0.07131811233513297</v>
+        <v>0.07131809492872576</v>
       </c>
       <c r="C9" s="1">
-        <v>0.07501569415959697</v>
+        <v>0.07501567669311315</v>
       </c>
       <c r="D9" s="1">
-        <v>0.06981911240614602</v>
+        <v>0.06981911041443878</v>
       </c>
       <c r="E9" s="1">
-        <v>0.07672064779432697</v>
+        <v>0.07672062522383749</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -271,16 +271,16 @@
         </is>
       </c>
       <c r="B10" s="1">
-        <v>0.01172032135908996</v>
+        <v>0.01172032913814469</v>
       </c>
       <c r="C10" s="1">
-        <v>0.02014078018017185</v>
+        <v>0.02014078802397035</v>
       </c>
       <c r="D10" s="1">
-        <v>0.02426740697417418</v>
+        <v>0.02426734783161422</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01875736131405326</v>
+        <v>0.01875739130038356</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -295,16 +295,16 @@
         </is>
       </c>
       <c r="B11" s="1">
-        <v>0.01166436280053529</v>
+        <v>0.01166436694925865</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.001187425107066598</v>
+        <v>-0.001187421011046852</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.004492457278143069</v>
+        <v>-0.004492382346648616</v>
       </c>
       <c r="E11" s="1">
-        <v>-8.422169188504469e-05</v>
+        <v>-8.424117964411781e-05</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -319,16 +319,16 @@
         </is>
       </c>
       <c r="B12" s="1">
-        <v>0.05056190453239551</v>
+        <v>0.05056190336976485</v>
       </c>
       <c r="C12" s="1">
-        <v>0.04306511931353163</v>
+        <v>0.04306511815919678</v>
       </c>
       <c r="D12" s="1">
-        <v>0.03904012692536307</v>
+        <v>0.03904010182921303</v>
       </c>
       <c r="E12" s="1">
-        <v>0.044410290250674</v>
+        <v>0.04441029709841615</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -343,16 +343,16 @@
         </is>
       </c>
       <c r="B13" s="1">
-        <v>0.07355902411024573</v>
+        <v>0.0735589997215651</v>
       </c>
       <c r="C13" s="1">
-        <v>0.06663037079653833</v>
+        <v>0.06663034656525979</v>
       </c>
       <c r="D13" s="1">
-        <v>0.07878106091421655</v>
+        <v>0.07878100736579507</v>
       </c>
       <c r="E13" s="1">
-        <v>0.06259113492093893</v>
+        <v>0.06259112018290036</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>d527da8625755b4774c7423c97275c86e56dd3fbd0960e5d9962779502e420ba</t>
+          <t>0db2b61560d1e414365fe9bf26d5b65bed568421a07cfe32bf0fe1501c3c2270</t>
         </is>
       </c>
     </row>
